--- a/addresses/matrix_0_20260426_230253.xlsx
+++ b/addresses/matrix_0_20260426_230253.xlsx
@@ -390,7 +390,9 @@
   <cols>
     <col min="1" max="1" width="20.796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5" customWidth="1"/>
+    <col min="5" max="5" width="17.8984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.69921875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.796875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="15.796875" bestFit="1" customWidth="1"/>
